--- a/src/src/main/webapp/portal/uaa/orgInfo/APM_Org_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/orgInfo/APM_Org_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/webapp/portal/uaa/orgInfo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -41,16 +41,16 @@
     <t>科室</t>
   </si>
   <si>
-    <t>Digital Healthcare</t>
+    <t>集团A</t>
   </si>
   <si>
-    <t>新增医院</t>
+    <t>医院A</t>
   </si>
   <si>
-    <t>新增院区1</t>
+    <t>院区A</t>
   </si>
   <si>
-    <t>新增科室1</t>
+    <t>科室A</t>
   </si>
 </sst>
 </file>

--- a/src/src/main/webapp/portal/uaa/orgInfo/APM_Org_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/orgInfo/APM_Org_Template.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="28810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\orgInfo\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{2A9F0B98-CE00-4C46-8F2D-0AE33A54A108}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="15960" windowHeight="18075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>集团</t>
   </si>
@@ -52,11 +53,14 @@
   <si>
     <t>科室A</t>
   </si>
+  <si>
+    <t>UUID</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -113,8 +117,36 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleMedium7"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultPivotStyle="PivotStyleMedium7">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{56D3FAAF-7C1D-40AC-8DB6-12F9349AF0F7}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -186,6 +218,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1277,18 +1312,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="1" customWidth="1"/>
-    <col min="5" max="248" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
+    <col min="5" max="248" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1301,8 +1336,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1315,6 +1353,7 @@
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="E2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/src/main/webapp/portal/uaa/orgInfo/APM_Org_Template.xlsx
+++ b/src/src/main/webapp/portal/uaa/orgInfo/APM_Org_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\orgInfo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git-apm\hc-apm-web\src\src\main\webapp\portal\uaa\orgInfo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{2A9F0B98-CE00-4C46-8F2D-0AE33A54A108}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83C5E5F-89EE-463B-8620-E8ACFDB1B2C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="465" windowWidth="15960" windowHeight="18075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3288" yWindow="2802" windowWidth="17280" windowHeight="8994" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>集团</t>
   </si>
@@ -56,16 +56,32 @@
   <si>
     <t>UUID</t>
   </si>
+  <si>
+    <t>UCMID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -109,10 +125,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1313,17 +1330,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
-    <col min="5" max="248" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.27734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.71875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="1" customWidth="1"/>
+    <col min="5" max="248" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1339,8 +1356,11 @@
       <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1354,10 +1374,12 @@
         <v>7</v>
       </c>
       <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
